--- a/docs/launch-campaign/oslsr-public-core-v1.xlsx
+++ b/docs/launch-campaign/oslsr-public-core-v1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="396">
   <si>
     <t>type</t>
   </si>
@@ -193,15 +193,6 @@
   </si>
   <si>
     <t>NIN must be exactly 11 digits</t>
-  </si>
-  <si>
-    <t>select_one lga_list</t>
-  </si>
-  <si>
-    <t>lga_id</t>
-  </si>
-  <si>
-    <t>Local Government Area (LGA)</t>
   </si>
   <si>
     <t>grp_labor</t>
@@ -1586,7 +1577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2070,16 +2061,16 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -2096,19 +2087,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="F21" t="s">
         <v>10</v>
@@ -2122,7 +2113,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
         <v>63</v>
@@ -2131,7 +2122,7 @@
         <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E22" t="s">
         <v>65</v>
@@ -2148,19 +2139,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
         <v>30</v>
       </c>
       <c r="E23" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F23" t="s">
         <v>10</v>
@@ -2186,7 +2177,7 @@
         <v>30</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F24" t="s">
         <v>10</v>
@@ -2200,19 +2191,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>68</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
         <v>10</v>
@@ -2226,19 +2217,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s">
         <v>10</v>
@@ -2252,7 +2243,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
         <v>75</v>
@@ -2264,7 +2255,7 @@
         <v>10</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
         <v>10</v>
@@ -2278,16 +2269,16 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
         <v>78</v>
       </c>
-      <c r="C28" t="s">
-        <v>79</v>
-      </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -2304,7 +2295,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="B29" t="s">
         <v>80</v>
@@ -2330,13 +2321,13 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
         <v>82</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>83</v>
-      </c>
-      <c r="C30" t="s">
-        <v>84</v>
       </c>
       <c r="D30" t="s">
         <v>30</v>
@@ -2348,21 +2339,21 @@
         <v>10</v>
       </c>
       <c r="G30" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="H30" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" t="s">
         <v>85</v>
-      </c>
-      <c r="C31" t="s">
-        <v>86</v>
       </c>
       <c r="D31" t="s">
         <v>30</v>
@@ -2374,10 +2365,10 @@
         <v>10</v>
       </c>
       <c r="G31" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="H31" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -2385,10 +2376,10 @@
         <v>27</v>
       </c>
       <c r="B32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" t="s">
         <v>87</v>
-      </c>
-      <c r="C32" t="s">
-        <v>88</v>
       </c>
       <c r="D32" t="s">
         <v>30</v>
@@ -2408,65 +2399,65 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" t="s">
         <v>89</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>90</v>
       </c>
-      <c r="D33" t="s">
-        <v>30</v>
-      </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="F33" t="s">
         <v>10</v>
       </c>
       <c r="G33" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="E34" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="F34" t="s">
         <v>10</v>
       </c>
       <c r="G34" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="H34" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -2486,7 +2477,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
@@ -2495,7 +2486,7 @@
         <v>98</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -2512,16 +2503,16 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
         <v>99</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>100</v>
       </c>
-      <c r="C37" t="s">
-        <v>101</v>
-      </c>
       <c r="D37" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
@@ -2530,24 +2521,24 @@
         <v>10</v>
       </c>
       <c r="G37" t="s">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="H37" t="s">
-        <v>10</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>10</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -2556,21 +2547,21 @@
         <v>10</v>
       </c>
       <c r="G38" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="H38" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>10</v>
+        <v>102</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -2590,13 +2581,13 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B40" t="s">
+        <v>103</v>
+      </c>
+      <c r="C40" t="s">
         <v>104</v>
-      </c>
-      <c r="C40" t="s">
-        <v>105</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -2616,16 +2607,16 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" t="s">
         <v>106</v>
       </c>
-      <c r="C41" t="s">
-        <v>107</v>
-      </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
@@ -2645,16 +2636,16 @@
         <v>27</v>
       </c>
       <c r="B42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C42" t="s">
         <v>108</v>
-      </c>
-      <c r="C42" t="s">
-        <v>109</v>
       </c>
       <c r="D42" t="s">
         <v>30</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="F42" t="s">
         <v>10</v>
@@ -2668,19 +2659,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="C43" t="s">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>112</v>
+        <v>10</v>
       </c>
       <c r="F43" t="s">
         <v>10</v>
@@ -2689,38 +2680,12 @@
         <v>10</v>
       </c>
       <c r="H43" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H44" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2731,7 +2696,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2742,1492 +2707,1492 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s">
         <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
         <v>117</v>
       </c>
-      <c r="B5" t="s">
-        <v>120</v>
-      </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" t="s">
         <v>124</v>
       </c>
-      <c r="B8" t="s">
-        <v>127</v>
-      </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B11" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C11" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" t="s">
         <v>135</v>
       </c>
-      <c r="B13" t="s">
-        <v>138</v>
-      </c>
       <c r="C13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C14" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C15" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C17" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C20" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>151</v>
+      </c>
+      <c r="B22" t="s">
         <v>154</v>
       </c>
-      <c r="B22" t="s">
-        <v>157</v>
-      </c>
       <c r="C22" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C26" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" t="s">
         <v>164</v>
       </c>
-      <c r="B27" t="s">
-        <v>167</v>
-      </c>
       <c r="C27" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C28" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B29" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C30" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B31" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C32" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" t="s">
         <v>177</v>
       </c>
-      <c r="B33" t="s">
-        <v>180</v>
-      </c>
       <c r="C33" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C34" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C35" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C36" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C37" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>185</v>
+      </c>
+      <c r="B38" t="s">
         <v>188</v>
       </c>
-      <c r="B38" t="s">
-        <v>191</v>
-      </c>
       <c r="C38" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B39" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C39" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C40" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" t="s">
         <v>195</v>
       </c>
-      <c r="B41" t="s">
-        <v>198</v>
-      </c>
       <c r="C41" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B44" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C44" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B45" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C45" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C46" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B47" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C47" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B48" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C48" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B49" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C49" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B50" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C50" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B51" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C51" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B52" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C52" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B53" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C53" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B54" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C54" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B55" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C55" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B56" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C56" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B57" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C57" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C58" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B59" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C59" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B60" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C60" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B61" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C61" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B62" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C62" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B63" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C63" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B64" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C64" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B65" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C65" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B66" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C66" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B67" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C67" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B68" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C68" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B69" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C69" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B70" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C70" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B71" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B72" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B73" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C73" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>259</v>
+      </c>
+      <c r="B74" t="s">
         <v>262</v>
       </c>
-      <c r="B74" t="s">
-        <v>265</v>
-      </c>
       <c r="C74" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B75" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C75" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B76" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C76" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B77" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C77" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B78" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C78" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B79" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C79" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B80" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C80" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B81" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C81" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B82" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C82" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B83" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C83" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B84" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C84" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B85" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C85" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B86" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C86" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B87" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C87" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B88" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C88" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B89" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C89" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B90" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C90" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B91" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C91" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B92" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C92" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B93" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C93" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B94" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C94" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B95" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C95" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B96" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C96" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B97" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C97" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B98" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C98" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B99" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C99" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B100" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C100" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B101" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C101" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B102" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C102" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B103" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C103" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B104" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C104" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B105" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C105" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B106" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C106" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B107" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C107" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B108" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C108" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B109" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C109" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B110" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C110" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B111" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C111" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B112" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C112" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B113" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C113" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B114" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C114" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B115" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C115" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B116" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C116" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B117" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C117" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B118" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C118" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B119" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C119" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B120" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C120" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B121" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C121" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B122" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C122" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B123" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C123" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B124" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C124" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B125" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C125" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B126" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C126" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B127" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C127" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B128" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C128" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B129" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C129" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B130" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C130" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B131" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C131" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B132" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C132" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B133" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C133" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B134" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C134" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>382</v>
+      </c>
+      <c r="B135" t="s">
         <v>385</v>
       </c>
-      <c r="B135" t="s">
-        <v>388</v>
-      </c>
       <c r="C135" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B136" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C136" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -4238,34 +4203,34 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1" t="s">
         <v>391</v>
-      </c>
-      <c r="B1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C1" t="s">
-        <v>393</v>
-      </c>
-      <c r="D1" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D2" t="s">
         <v>395</v>
-      </c>
-      <c r="B2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D2" t="s">
-        <v>398</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/docs/launch-campaign/oslsr-public-core-v1.xlsx
+++ b/docs/launch-campaign/oslsr-public-core-v1.xlsx
@@ -400,16 +400,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H44"/>
-  <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="80.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="50.83203125" customWidth="1"/>
-    <col min="6" max="6" width="55.83203125" customWidth="1"/>
-    <col min="7" max="7" width="45.83203125" customWidth="1"/>
-    <col min="8" max="8" width="35.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1564,12 +1554,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C136"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="50.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:C225"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2489,10 +2474,10 @@
         <v>skill_list</v>
       </c>
       <c r="B84" t="str">
-        <v>auto_mechanic</v>
+        <v>pop_plastering</v>
       </c>
       <c r="C84" t="str">
-        <v>Auto Mechanic</v>
+        <v>POP/Plaster of Paris Work</v>
       </c>
     </row>
     <row r="85">
@@ -2500,10 +2485,10 @@
         <v>skill_list</v>
       </c>
       <c r="B85" t="str">
-        <v>auto_electrician</v>
+        <v>auto_mechanic</v>
       </c>
       <c r="C85" t="str">
-        <v>Auto Electrician</v>
+        <v>Auto Mechanic</v>
       </c>
     </row>
     <row r="86">
@@ -2511,10 +2496,10 @@
         <v>skill_list</v>
       </c>
       <c r="B86" t="str">
-        <v>panel_beating</v>
+        <v>auto_electrician</v>
       </c>
       <c r="C86" t="str">
-        <v>Panel Beating &amp; Spray Painting</v>
+        <v>Auto Electrician</v>
       </c>
     </row>
     <row r="87">
@@ -2522,10 +2507,10 @@
         <v>skill_list</v>
       </c>
       <c r="B87" t="str">
-        <v>vulcanizing</v>
+        <v>panel_beating</v>
       </c>
       <c r="C87" t="str">
-        <v>Vulcanizing/Tire Services</v>
+        <v>Panel Beating &amp; Spray Painting</v>
       </c>
     </row>
     <row r="88">
@@ -2533,10 +2518,10 @@
         <v>skill_list</v>
       </c>
       <c r="B88" t="str">
-        <v>motorcycle_repair</v>
+        <v>vulcanizing</v>
       </c>
       <c r="C88" t="str">
-        <v>Motorcycle/Tricycle Repair</v>
+        <v>Vulcanizing/Tire Services</v>
       </c>
     </row>
     <row r="89">
@@ -2544,10 +2529,10 @@
         <v>skill_list</v>
       </c>
       <c r="B89" t="str">
-        <v>heavy_equipment</v>
+        <v>motorcycle_repair</v>
       </c>
       <c r="C89" t="str">
-        <v>Heavy Equipment Operation</v>
+        <v>Motorcycle/Tricycle Repair</v>
       </c>
     </row>
     <row r="90">
@@ -2555,10 +2540,10 @@
         <v>skill_list</v>
       </c>
       <c r="B90" t="str">
-        <v>generator_repair</v>
+        <v>heavy_equipment</v>
       </c>
       <c r="C90" t="str">
-        <v>Generator Repair</v>
+        <v>Heavy Equipment Operation</v>
       </c>
     </row>
     <row r="91">
@@ -2566,10 +2551,10 @@
         <v>skill_list</v>
       </c>
       <c r="B91" t="str">
-        <v>tailoring</v>
+        <v>generator_repair</v>
       </c>
       <c r="C91" t="str">
-        <v>Tailoring/Sewing</v>
+        <v>Generator Repair</v>
       </c>
     </row>
     <row r="92">
@@ -2577,10 +2562,10 @@
         <v>skill_list</v>
       </c>
       <c r="B92" t="str">
-        <v>fashion_design</v>
+        <v>battery_inverter</v>
       </c>
       <c r="C92" t="str">
-        <v>Fashion Design</v>
+        <v>Battery/Inverter Technician</v>
       </c>
     </row>
     <row r="93">
@@ -2588,10 +2573,10 @@
         <v>skill_list</v>
       </c>
       <c r="B93" t="str">
-        <v>hairdressing</v>
+        <v>tailoring</v>
       </c>
       <c r="C93" t="str">
-        <v>Hairdressing/Styling</v>
+        <v>Tailoring/Sewing</v>
       </c>
     </row>
     <row r="94">
@@ -2599,10 +2584,10 @@
         <v>skill_list</v>
       </c>
       <c r="B94" t="str">
-        <v>barbing</v>
+        <v>fashion_design</v>
       </c>
       <c r="C94" t="str">
-        <v>Barbing</v>
+        <v>Fashion Design</v>
       </c>
     </row>
     <row r="95">
@@ -2610,10 +2595,10 @@
         <v>skill_list</v>
       </c>
       <c r="B95" t="str">
-        <v>makeup</v>
+        <v>hairdressing</v>
       </c>
       <c r="C95" t="str">
-        <v>Makeup Artistry</v>
+        <v>Hairdressing/Styling</v>
       </c>
     </row>
     <row r="96">
@@ -2621,10 +2606,10 @@
         <v>skill_list</v>
       </c>
       <c r="B96" t="str">
-        <v>shoe_making</v>
+        <v>barbing</v>
       </c>
       <c r="C96" t="str">
-        <v>Shoe Making/Cobbling</v>
+        <v>Barbing</v>
       </c>
     </row>
     <row r="97">
@@ -2632,10 +2617,10 @@
         <v>skill_list</v>
       </c>
       <c r="B97" t="str">
-        <v>bag_making</v>
+        <v>makeup</v>
       </c>
       <c r="C97" t="str">
-        <v>Bag Making/Leather Craft</v>
+        <v>Makeup Artistry</v>
       </c>
     </row>
     <row r="98">
@@ -2643,10 +2628,10 @@
         <v>skill_list</v>
       </c>
       <c r="B98" t="str">
-        <v>jewelry</v>
+        <v>shoe_making</v>
       </c>
       <c r="C98" t="str">
-        <v>Jewelry Making</v>
+        <v>Shoe Making/Cobbling</v>
       </c>
     </row>
     <row r="99">
@@ -2654,10 +2639,10 @@
         <v>skill_list</v>
       </c>
       <c r="B99" t="str">
-        <v>farming</v>
+        <v>bag_making</v>
       </c>
       <c r="C99" t="str">
-        <v>Crop Farming</v>
+        <v>Bag Making/Leather Craft</v>
       </c>
     </row>
     <row r="100">
@@ -2665,10 +2650,10 @@
         <v>skill_list</v>
       </c>
       <c r="B100" t="str">
-        <v>livestock</v>
+        <v>jewelry</v>
       </c>
       <c r="C100" t="str">
-        <v>Livestock/Poultry Farming</v>
+        <v>Jewelry Making</v>
       </c>
     </row>
     <row r="101">
@@ -2676,10 +2661,10 @@
         <v>skill_list</v>
       </c>
       <c r="B101" t="str">
-        <v>fishery</v>
+        <v>nail_technology</v>
       </c>
       <c r="C101" t="str">
-        <v>Fishery/Aquaculture</v>
+        <v>Nail Technology</v>
       </c>
     </row>
     <row r="102">
@@ -2687,10 +2672,10 @@
         <v>skill_list</v>
       </c>
       <c r="B102" t="str">
-        <v>catering</v>
+        <v>farming</v>
       </c>
       <c r="C102" t="str">
-        <v>Catering/Event Cooking</v>
+        <v>Crop Farming</v>
       </c>
     </row>
     <row r="103">
@@ -2698,10 +2683,10 @@
         <v>skill_list</v>
       </c>
       <c r="B103" t="str">
-        <v>baking</v>
+        <v>livestock</v>
       </c>
       <c r="C103" t="str">
-        <v>Baking &amp; Confectionery</v>
+        <v>Livestock/Poultry Farming</v>
       </c>
     </row>
     <row r="104">
@@ -2709,10 +2694,10 @@
         <v>skill_list</v>
       </c>
       <c r="B104" t="str">
-        <v>food_processing</v>
+        <v>fishery</v>
       </c>
       <c r="C104" t="str">
-        <v>Food Processing/Preservation</v>
+        <v>Fishery/Aquaculture</v>
       </c>
     </row>
     <row r="105">
@@ -2720,10 +2705,10 @@
         <v>skill_list</v>
       </c>
       <c r="B105" t="str">
-        <v>butchery</v>
+        <v>catering</v>
       </c>
       <c r="C105" t="str">
-        <v>Butchery/Meat Processing</v>
+        <v>Catering/Event Cooking</v>
       </c>
     </row>
     <row r="106">
@@ -2731,10 +2716,10 @@
         <v>skill_list</v>
       </c>
       <c r="B106" t="str">
-        <v>software_dev</v>
+        <v>baking</v>
       </c>
       <c r="C106" t="str">
-        <v>Software Development</v>
+        <v>Baking &amp; Confectionery</v>
       </c>
     </row>
     <row r="107">
@@ -2742,10 +2727,10 @@
         <v>skill_list</v>
       </c>
       <c r="B107" t="str">
-        <v>web_design</v>
+        <v>food_processing</v>
       </c>
       <c r="C107" t="str">
-        <v>Web Design/Development</v>
+        <v>Food Processing/Preservation</v>
       </c>
     </row>
     <row r="108">
@@ -2753,10 +2738,10 @@
         <v>skill_list</v>
       </c>
       <c r="B108" t="str">
-        <v>graphic_design</v>
+        <v>butchery</v>
       </c>
       <c r="C108" t="str">
-        <v>Graphic Design</v>
+        <v>Butchery/Meat Processing</v>
       </c>
     </row>
     <row r="109">
@@ -2764,10 +2749,10 @@
         <v>skill_list</v>
       </c>
       <c r="B109" t="str">
-        <v>video_editing</v>
+        <v>agro_processing</v>
       </c>
       <c r="C109" t="str">
-        <v>Video Editing/Production</v>
+        <v>Agro-Processing Equipment Operation</v>
       </c>
     </row>
     <row r="110">
@@ -2775,10 +2760,10 @@
         <v>skill_list</v>
       </c>
       <c r="B110" t="str">
-        <v>data_entry</v>
+        <v>horticulture</v>
       </c>
       <c r="C110" t="str">
-        <v>Data Entry/Typing</v>
+        <v>Horticulture/Floriculture</v>
       </c>
     </row>
     <row r="111">
@@ -2786,10 +2771,10 @@
         <v>skill_list</v>
       </c>
       <c r="B111" t="str">
-        <v>accounting</v>
+        <v>software_dev</v>
       </c>
       <c r="C111" t="str">
-        <v>Accounting/Bookkeeping</v>
+        <v>Software Development</v>
       </c>
     </row>
     <row r="112">
@@ -2797,10 +2782,10 @@
         <v>skill_list</v>
       </c>
       <c r="B112" t="str">
-        <v>office_admin</v>
+        <v>web_design</v>
       </c>
       <c r="C112" t="str">
-        <v>Office Administration</v>
+        <v>Web Design/Development</v>
       </c>
     </row>
     <row r="113">
@@ -2808,10 +2793,10 @@
         <v>skill_list</v>
       </c>
       <c r="B113" t="str">
-        <v>computer_repair</v>
+        <v>graphic_design</v>
       </c>
       <c r="C113" t="str">
-        <v>Computer/Phone Repair</v>
+        <v>Graphic Design</v>
       </c>
     </row>
     <row r="114">
@@ -2819,10 +2804,10 @@
         <v>skill_list</v>
       </c>
       <c r="B114" t="str">
-        <v>social_media</v>
+        <v>video_editing</v>
       </c>
       <c r="C114" t="str">
-        <v>Social Media Management</v>
+        <v>Video Editing/Production</v>
       </c>
     </row>
     <row r="115">
@@ -2830,10 +2815,10 @@
         <v>skill_list</v>
       </c>
       <c r="B115" t="str">
-        <v>nursing</v>
+        <v>data_entry</v>
       </c>
       <c r="C115" t="str">
-        <v>Nursing/Patient Care</v>
+        <v>Data Entry/Typing</v>
       </c>
     </row>
     <row r="116">
@@ -2841,10 +2826,10 @@
         <v>skill_list</v>
       </c>
       <c r="B116" t="str">
-        <v>pharmacy_tech</v>
+        <v>accounting</v>
       </c>
       <c r="C116" t="str">
-        <v>Pharmacy Assistant</v>
+        <v>Accounting/Bookkeeping</v>
       </c>
     </row>
     <row r="117">
@@ -2852,10 +2837,10 @@
         <v>skill_list</v>
       </c>
       <c r="B117" t="str">
-        <v>lab_tech</v>
+        <v>office_admin</v>
       </c>
       <c r="C117" t="str">
-        <v>Laboratory Technician</v>
+        <v>Office Administration</v>
       </c>
     </row>
     <row r="118">
@@ -2863,10 +2848,10 @@
         <v>skill_list</v>
       </c>
       <c r="B118" t="str">
-        <v>community_health</v>
+        <v>computer_repair</v>
       </c>
       <c r="C118" t="str">
-        <v>Community Health Worker</v>
+        <v>Computer/Phone Repair</v>
       </c>
     </row>
     <row r="119">
@@ -2874,10 +2859,10 @@
         <v>skill_list</v>
       </c>
       <c r="B119" t="str">
-        <v>caregiving</v>
+        <v>social_media</v>
       </c>
       <c r="C119" t="str">
-        <v>Elderly/Child Caregiving</v>
+        <v>Social Media Management</v>
       </c>
     </row>
     <row r="120">
@@ -2885,10 +2870,10 @@
         <v>skill_list</v>
       </c>
       <c r="B120" t="str">
-        <v>physiotherapy</v>
+        <v>digital_marketing</v>
       </c>
       <c r="C120" t="str">
-        <v>Physiotherapy Assistant</v>
+        <v>Digital Marketing/SEO</v>
       </c>
     </row>
     <row r="121">
@@ -2896,10 +2881,10 @@
         <v>skill_list</v>
       </c>
       <c r="B121" t="str">
-        <v>teaching</v>
+        <v>nursing</v>
       </c>
       <c r="C121" t="str">
-        <v>Teaching/Tutoring</v>
+        <v>Nursing/Patient Care</v>
       </c>
     </row>
     <row r="122">
@@ -2907,10 +2892,10 @@
         <v>skill_list</v>
       </c>
       <c r="B122" t="str">
-        <v>driving</v>
+        <v>pharmacy_tech</v>
       </c>
       <c r="C122" t="str">
-        <v>Professional Driving</v>
+        <v>Pharmacy Assistant</v>
       </c>
     </row>
     <row r="123">
@@ -2918,10 +2903,10 @@
         <v>skill_list</v>
       </c>
       <c r="B123" t="str">
-        <v>security</v>
+        <v>lab_tech</v>
       </c>
       <c r="C123" t="str">
-        <v>Security Services</v>
+        <v>Laboratory Technician</v>
       </c>
     </row>
     <row r="124">
@@ -2929,10 +2914,10 @@
         <v>skill_list</v>
       </c>
       <c r="B124" t="str">
-        <v>event_planning</v>
+        <v>community_health</v>
       </c>
       <c r="C124" t="str">
-        <v>Event Planning/Decoration</v>
+        <v>Community Health Worker</v>
       </c>
     </row>
     <row r="125">
@@ -2940,10 +2925,10 @@
         <v>skill_list</v>
       </c>
       <c r="B125" t="str">
-        <v>photography</v>
+        <v>caregiving</v>
       </c>
       <c r="C125" t="str">
-        <v>Photography/Videography</v>
+        <v>Elderly/Child Caregiving</v>
       </c>
     </row>
     <row r="126">
@@ -2951,10 +2936,10 @@
         <v>skill_list</v>
       </c>
       <c r="B126" t="str">
-        <v>cleaning</v>
+        <v>physiotherapy</v>
       </c>
       <c r="C126" t="str">
-        <v>Professional Cleaning</v>
+        <v>Physiotherapy Assistant</v>
       </c>
     </row>
     <row r="127">
@@ -2962,10 +2947,10 @@
         <v>skill_list</v>
       </c>
       <c r="B127" t="str">
-        <v>laundry</v>
+        <v>traditional_medicine</v>
       </c>
       <c r="C127" t="str">
-        <v>Laundry/Dry Cleaning</v>
+        <v>Traditional Medicine/Herbalism</v>
       </c>
     </row>
     <row r="128">
@@ -2973,10 +2958,10 @@
         <v>skill_list</v>
       </c>
       <c r="B128" t="str">
-        <v>furniture</v>
+        <v>dental_assistant</v>
       </c>
       <c r="C128" t="str">
-        <v>Furniture Making</v>
+        <v>Dental Assistant</v>
       </c>
     </row>
     <row r="129">
@@ -2984,10 +2969,10 @@
         <v>skill_list</v>
       </c>
       <c r="B129" t="str">
-        <v>upholstery</v>
+        <v>teaching</v>
       </c>
       <c r="C129" t="str">
-        <v>Upholstery</v>
+        <v>Teaching/Tutoring</v>
       </c>
     </row>
     <row r="130">
@@ -2995,10 +2980,10 @@
         <v>skill_list</v>
       </c>
       <c r="B130" t="str">
-        <v>pottery</v>
+        <v>driving</v>
       </c>
       <c r="C130" t="str">
-        <v>Pottery/Ceramics</v>
+        <v>Professional Driving</v>
       </c>
     </row>
     <row r="131">
@@ -3006,10 +2991,10 @@
         <v>skill_list</v>
       </c>
       <c r="B131" t="str">
-        <v>blacksmith</v>
+        <v>event_planning</v>
       </c>
       <c r="C131" t="str">
-        <v>Blacksmithing</v>
+        <v>Event Planning/Decoration</v>
       </c>
     </row>
     <row r="132">
@@ -3017,10 +3002,10 @@
         <v>skill_list</v>
       </c>
       <c r="B132" t="str">
-        <v>weaving</v>
+        <v>photography</v>
       </c>
       <c r="C132" t="str">
-        <v>Weaving/Textile Crafts</v>
+        <v>Photography/Videography</v>
       </c>
     </row>
     <row r="133">
@@ -3028,48 +3013,1027 @@
         <v>skill_list</v>
       </c>
       <c r="B133" t="str">
-        <v>sign_writing</v>
+        <v>cleaning</v>
       </c>
       <c r="C133" t="str">
-        <v>Sign Writing/Branding</v>
+        <v>Professional Cleaning</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>guardian_rel_list</v>
+        <v>skill_list</v>
       </c>
       <c r="B134" t="str">
-        <v>parent</v>
+        <v>laundry</v>
       </c>
       <c r="C134" t="str">
-        <v>Parent</v>
+        <v>Laundry/Dry Cleaning</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>guardian_rel_list</v>
+        <v>skill_list</v>
       </c>
       <c r="B135" t="str">
-        <v>legal_guardian</v>
+        <v>translation</v>
       </c>
       <c r="C135" t="str">
-        <v>Legal Guardian</v>
+        <v>Translation/Interpretation</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B136" t="str">
+        <v>paralegal</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Legal Clerk/Paralegal</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B137" t="str">
+        <v>furniture</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Furniture Making</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B138" t="str">
+        <v>upholstery</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Upholstery</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B139" t="str">
+        <v>pottery</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Pottery/Ceramics</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B140" t="str">
+        <v>blacksmith</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Blacksmithing</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B141" t="str">
+        <v>weaving</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Weaving/Textile Crafts</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B142" t="str">
+        <v>sign_writing</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Sign Writing/Branding</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B143" t="str">
+        <v>calabash_carving</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Calabash/Gourd Carving</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B144" t="str">
+        <v>commercial_driving</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Commercial Bus/Taxi Driving</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B145" t="str">
+        <v>okada_riding</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Motorcycle Taxi (Okada) Riding</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B146" t="str">
+        <v>keke_operation</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Tricycle (Keke) Operation</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B147" t="str">
+        <v>haulage_driving</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Truck/Haulage Driving</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B148" t="str">
+        <v>dispatch_courier</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Dispatch Riding/Courier</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B149" t="str">
+        <v>warehouse_management</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Warehouse Management</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B150" t="str">
+        <v>logistics_coordination</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Freight/Logistics Coordination</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B151" t="str">
+        <v>forklift_operation</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Forklift Operation</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B152" t="str">
+        <v>trading</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Trading/General Commerce</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B153" t="str">
+        <v>agrochemical_sales</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Agrochemical Sales</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B154" t="str">
+        <v>medical_sales</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Pharmaceutical/Medical Sales</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B155" t="str">
+        <v>building_materials_sales</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Building Materials Sales</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B156" t="str">
+        <v>electronics_sales</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Electronics/Phone Sales</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B157" t="str">
+        <v>fmcg_distribution</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Provisions/FMCG Distribution</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B158" t="str">
+        <v>fuel_retailing</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Fuel/Gas Retailing</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B159" t="str">
+        <v>auto_parts_sales</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Auto Parts Sales</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B160" t="str">
+        <v>quarrying</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Quarrying/Stone Cutting</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B161" t="str">
+        <v>sand_mining</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Sand Mining/Dredging</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B162" t="str">
+        <v>mineral_mining</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Gold/Mineral Artisan Mining</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B163" t="str">
+        <v>clay_extraction</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Clay/Kaolin Extraction</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B164" t="str">
+        <v>aggregate_processing</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Gravel/Aggregate Processing</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B165" t="str">
+        <v>soap_making</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Soap/Detergent Making</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B166" t="str">
+        <v>water_production</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Sachet/Bottled Water Production</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B167" t="str">
+        <v>block_making</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Block/Brick Making</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B168" t="str">
+        <v>paint_manufacturing</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Paint Manufacturing</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B169" t="str">
+        <v>plastic_recycling</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Plastic/Rubber Recycling</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B170" t="str">
+        <v>garment_factory</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Textile/Garment Factory Work</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B171" t="str">
+        <v>metal_fabrication</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Metal Fabrication/Foundry</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B172" t="str">
+        <v>printing_production</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Paper/Printing Production</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B173" t="str">
+        <v>hotel_management</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Hotel/Guest House Management</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B174" t="str">
+        <v>restaurant_management</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Restaurant/Bar Management</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B175" t="str">
+        <v>bartending</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Bartending/Mixology</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B176" t="str">
+        <v>tour_guide</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Tour Guide Services</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B177" t="str">
+        <v>event_centre_management</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Event Centre Management</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B178" t="str">
+        <v>apartment_hosting</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Short-Let/Apartment Hosting</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B179" t="str">
+        <v>chef</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Chef/Professional Cooking</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B180" t="str">
+        <v>music_production</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Music Production/DJ</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B181" t="str">
+        <v>acting</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Acting/Theatre Performance</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B182" t="str">
+        <v>comedy_mc</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Comedy/MC/Entertainment</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B183" t="str">
+        <v>dance</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Dance/Choreography</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B184" t="str">
+        <v>sound_engineering</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Sound Engineering</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B185" t="str">
+        <v>instrument_playing</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Musical Instrument Playing</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B186" t="str">
+        <v>fine_art</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Fine Art/Painting</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B187" t="str">
+        <v>animation</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Animation/Motion Graphics</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B188" t="str">
+        <v>security</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Private Security Guard</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B189" t="str">
+        <v>cctv_installation</v>
+      </c>
+      <c r="C189" t="str">
+        <v>CCTV/Surveillance Installation</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B190" t="str">
+        <v>fire_safety</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Fire Safety/Extinguisher Services</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B191" t="str">
+        <v>locksmith</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Locksmith Services</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B192" t="str">
+        <v>dog_training</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Dog Training/K9 Handler</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B193" t="str">
+        <v>crowd_management</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Traffic/Crowd Management</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B194" t="str">
+        <v>waste_collection</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Waste Collection/Disposal</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B195" t="str">
+        <v>scrap_dealing</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Recycling/Scrap Dealing</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B196" t="str">
+        <v>pest_control</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Fumigation/Pest Control</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B197" t="str">
+        <v>drainage_services</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Sewage/Drainage Services</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B198" t="str">
+        <v>environmental_remediation</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Environmental Remediation</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B199" t="str">
+        <v>clergy</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Religious Leadership/Clergy</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B200" t="str">
+        <v>islamic_teaching</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Quranic/Islamic Teaching</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B201" t="str">
+        <v>choir_direction</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Church Music/Choir Direction</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B202" t="str">
+        <v>community_development</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Community Development Work</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B203" t="str">
+        <v>counselling</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Counselling Services</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B204" t="str">
+        <v>borehole_drilling</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Borehole Drilling</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B205" t="str">
+        <v>water_treatment</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Water Treatment/Purification</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B206" t="str">
+        <v>power_line_work</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Electrical Power Line Work</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B207" t="str">
+        <v>gas_pipeline</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Gas Pipeline Fitting</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B208" t="str">
+        <v>engine_servicing</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Diesel/Petrol Engine Servicing</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B209" t="str">
+        <v>renewable_energy</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Renewable Energy Technician</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B210" t="str">
+        <v>boat_building</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Boat Building/Repair</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B211" t="str">
+        <v>river_fishing</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Fishing (River/Lake)</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B212" t="str">
+        <v>boat_operation</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Canoe/Boat Operation</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B213" t="str">
+        <v>fish_smoking</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Fish Smoking/Drying</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B214" t="str">
+        <v>pond_construction</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Pond/Dam Construction</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B215" t="str">
+        <v>estate_agency</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Property/Estate Agency</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B216" t="str">
+        <v>land_surveying</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Land Surveying</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B217" t="str">
+        <v>quantity_surveying</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Building/Quantity Surveying</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B218" t="str">
+        <v>architecture</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Architecture/Draughtsmanship</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B219" t="str">
+        <v>interior_design</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Interior Design/Decoration</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B220" t="str">
+        <v>facility_management</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Facility Management</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B221" t="str">
+        <v>pool_maintenance</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Swimming Pool Construction/Maintenance</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B222" t="str">
+        <v>storage_construction</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Pest-Proof Storage Construction</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
         <v>guardian_rel_list</v>
       </c>
-      <c r="B136" t="str">
+      <c r="B223" t="str">
+        <v>parent</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Parent</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>guardian_rel_list</v>
+      </c>
+      <c r="B224" t="str">
+        <v>legal_guardian</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Legal Guardian</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>guardian_rel_list</v>
+      </c>
+      <c r="B225" t="str">
         <v>other</v>
       </c>
-      <c r="C136" t="str">
+      <c r="C225" t="str">
         <v>Other (relative or caregiver)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C136"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C225"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3077,12 +4041,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D2"/>
-  <cols>
-    <col min="1" max="1" width="45.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">

--- a/docs/launch-campaign/oslsr-public-core-v1.xlsx
+++ b/docs/launch-campaign/oslsr-public-core-v1.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H43"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -507,13 +507,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>geopoint</v>
+        <v>calculate</v>
       </c>
       <c r="B5" t="str">
-        <v>gps_location</v>
+        <v>form_mode</v>
       </c>
       <c r="C5" t="str">
-        <v>GPS Location</v>
+        <v/>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -522,7 +522,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>once(if(${device_id} != null, 'enumerator', 'public'))</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -533,13 +533,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>calculate</v>
+        <v>begin_group</v>
       </c>
       <c r="B6" t="str">
-        <v>form_mode</v>
+        <v>grp_intro</v>
       </c>
       <c r="C6" t="str">
-        <v/>
+        <v>Introduction &amp; Consent</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -548,7 +548,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>once(if(${device_id} != null, 'enumerator', 'public'))</v>
+        <v/>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -559,13 +559,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>begin_group</v>
+        <v>note</v>
       </c>
       <c r="B7" t="str">
-        <v>grp_intro</v>
+        <v>note_intro</v>
       </c>
       <c r="C7" t="str">
-        <v>Introduction &amp; Consent</v>
+        <v>Welcome to the Oyo State Labour &amp; Skills Registry (OSLSR). This survey takes approximately 10 minutes.</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -585,16 +585,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>note</v>
+        <v>select_one yes_no</v>
       </c>
       <c r="B8" t="str">
-        <v>note_intro</v>
+        <v>consent_basic</v>
       </c>
       <c r="C8" t="str">
-        <v>Welcome to the Oyo State Labour &amp; Skills Registry (OSLSR). This survey takes approximately 10 minutes.</v>
+        <v>Do you consent to participate in this survey?</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -611,16 +611,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>select_one yes_no</v>
+        <v>end_group</v>
       </c>
       <c r="B9" t="str">
-        <v>consent_basic</v>
+        <v/>
       </c>
       <c r="C9" t="str">
-        <v>Do you consent to participate in this survey?</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -637,19 +637,19 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>end_group</v>
+        <v>begin_group</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>grp_identity</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>Identity &amp; Demographics</v>
       </c>
       <c r="D10" t="str">
         <v/>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>${consent_basic} = 'yes'</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -663,19 +663,19 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>begin_group</v>
+        <v>text</v>
       </c>
       <c r="B11" t="str">
-        <v>grp_identity</v>
+        <v>surname</v>
       </c>
       <c r="C11" t="str">
-        <v>Identity &amp; Demographics</v>
+        <v>Surname</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="E11" t="str">
-        <v>${consent_basic} = 'yes'</v>
+        <v/>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -692,10 +692,10 @@
         <v>text</v>
       </c>
       <c r="B12" t="str">
-        <v>surname</v>
+        <v>firstname</v>
       </c>
       <c r="C12" t="str">
-        <v>Surname</v>
+        <v>First Name</v>
       </c>
       <c r="D12" t="str">
         <v>yes</v>
@@ -715,13 +715,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>text</v>
+        <v>select_one gender_list</v>
       </c>
       <c r="B13" t="str">
-        <v>firstname</v>
+        <v>gender</v>
       </c>
       <c r="C13" t="str">
-        <v>First Name</v>
+        <v>Gender</v>
       </c>
       <c r="D13" t="str">
         <v>yes</v>
@@ -741,13 +741,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>select_one gender_list</v>
+        <v>date</v>
       </c>
       <c r="B14" t="str">
-        <v>gender</v>
+        <v>dob</v>
       </c>
       <c r="C14" t="str">
-        <v>Gender</v>
+        <v>Date of Birth</v>
       </c>
       <c r="D14" t="str">
         <v>yes</v>
@@ -759,62 +759,62 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>. &lt;= today()</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Cannot be a future date</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>date</v>
+        <v>calculate</v>
       </c>
       <c r="B15" t="str">
-        <v>dob</v>
+        <v>age</v>
       </c>
       <c r="C15" t="str">
-        <v>Date of Birth</v>
+        <v/>
       </c>
       <c r="D15" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v/>
+        <v>int((today() - ${dob}) div 365.25)</v>
       </c>
       <c r="G15" t="str">
-        <v>. &lt;= today()</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v>Cannot be a future date</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>calculate</v>
+        <v>text</v>
       </c>
       <c r="B16" t="str">
-        <v>age</v>
+        <v>phone_number</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>Phone Number</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>int((today() - ${dob}) div 365.25)</v>
+        <v/>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>regex(., '^[0][7-9][0-1][0-9]{8}$')</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>Enter a valid Nigerian mobile number</v>
       </c>
     </row>
     <row r="17">
@@ -822,13 +822,13 @@
         <v>text</v>
       </c>
       <c r="B17" t="str">
-        <v>phone_number</v>
+        <v>email</v>
       </c>
       <c r="C17" t="str">
-        <v>Phone Number</v>
+        <v>Email address (optional) — we'll send your registration confirmation and reference number here</v>
       </c>
       <c r="D17" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -837,10 +837,10 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>regex(., '^[0][7-9][0-1][0-9]{8}$')</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v>Enter a valid Nigerian mobile number</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -848,13 +848,13 @@
         <v>text</v>
       </c>
       <c r="B18" t="str">
-        <v>email</v>
+        <v>nin</v>
       </c>
       <c r="C18" t="str">
-        <v>Email address (optional) — we'll send your registration confirmation and reference number here</v>
+        <v>National Identity Number (NIN)</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -863,21 +863,21 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>string-length(.) = 11 and regex(., '^[0-9]+$')</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>NIN must be exactly 11 digits</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>text</v>
+        <v>select_one lga_list</v>
       </c>
       <c r="B19" t="str">
-        <v>nin</v>
+        <v>lga_id</v>
       </c>
       <c r="C19" t="str">
-        <v>National Identity Number (NIN)</v>
+        <v>Local Government Area (LGA)</v>
       </c>
       <c r="D19" t="str">
         <v>yes</v>
@@ -889,24 +889,24 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>string-length(.) = 11 and regex(., '^[0-9]+$')</v>
+        <v/>
       </c>
       <c r="H19" t="str">
-        <v>NIN must be exactly 11 digits</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>select_one lga_list</v>
+        <v>end_group</v>
       </c>
       <c r="B20" t="str">
-        <v>lga_id</v>
+        <v/>
       </c>
       <c r="C20" t="str">
-        <v>Local Government Area (LGA)</v>
+        <v/>
       </c>
       <c r="D20" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -923,19 +923,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>end_group</v>
+        <v>begin_group</v>
       </c>
       <c r="B21" t="str">
-        <v/>
+        <v>grp_labor</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>Labour Force Participation</v>
       </c>
       <c r="D21" t="str">
         <v/>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>${age} &gt;= 15</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -949,19 +949,19 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>begin_group</v>
+        <v>text</v>
       </c>
       <c r="B22" t="str">
-        <v>grp_labor</v>
+        <v>main_occupation</v>
       </c>
       <c r="C22" t="str">
-        <v>Labour Force Participation</v>
+        <v>Main Occupation (e.g. tailor, farmer, trader, mechanic)</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="E22" t="str">
-        <v>${age} &gt;= 15</v>
+        <v/>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -975,13 +975,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>text</v>
+        <v>select_one emp_type</v>
       </c>
       <c r="B23" t="str">
-        <v>main_occupation</v>
+        <v>employment_type</v>
       </c>
       <c r="C23" t="str">
-        <v>Main Occupation/Job Title</v>
+        <v>Type of Employment</v>
       </c>
       <c r="D23" t="str">
         <v>yes</v>
@@ -1001,13 +1001,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>select_one emp_type</v>
+        <v>select_one experience_list</v>
       </c>
       <c r="B24" t="str">
-        <v>employment_type</v>
+        <v>years_experience</v>
       </c>
       <c r="C24" t="str">
-        <v>Type of Employment</v>
+        <v>Years of experience in this work</v>
       </c>
       <c r="D24" t="str">
         <v>yes</v>
@@ -1027,16 +1027,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>select_one experience_list</v>
+        <v>end_group</v>
       </c>
       <c r="B25" t="str">
-        <v>years_experience</v>
+        <v/>
       </c>
       <c r="C25" t="str">
-        <v>Years of Experience in Main Occupation</v>
+        <v/>
       </c>
       <c r="D25" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1053,19 +1053,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>end_group</v>
+        <v>begin_group</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>grp_guardian</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>Parent / Guardian Consent</v>
       </c>
       <c r="D26" t="str">
         <v/>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>${age} &lt; 15</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -1079,19 +1079,19 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>begin_group</v>
+        <v>note</v>
       </c>
       <c r="B27" t="str">
-        <v>grp_guardian</v>
+        <v>note_guardian</v>
       </c>
       <c r="C27" t="str">
-        <v>Parent / Guardian Consent</v>
+        <v>Because this registrant is under 15, a parent or guardian must give consent. A young person learning a trade under supervision (an apprentice) is welcome to register — this section captures the consent needed to include them safely.</v>
       </c>
       <c r="D27" t="str">
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>${age} &lt; 15</v>
+        <v/>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -1105,16 +1105,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>note</v>
+        <v>text</v>
       </c>
       <c r="B28" t="str">
-        <v>note_guardian</v>
+        <v>guardian_name</v>
       </c>
       <c r="C28" t="str">
-        <v>Because this registrant is under 15, a parent or guardian must give consent. A young person learning a trade under supervision (an apprentice) is welcome to register — this section captures the consent needed to include them safely.</v>
+        <v>Full name of the parent or guardian</v>
       </c>
       <c r="D28" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1131,13 +1131,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>text</v>
+        <v>select_one guardian_rel_list</v>
       </c>
       <c r="B29" t="str">
-        <v>guardian_name</v>
+        <v>guardian_relationship</v>
       </c>
       <c r="C29" t="str">
-        <v>Full name of the parent or guardian</v>
+        <v>Relationship to the young person</v>
       </c>
       <c r="D29" t="str">
         <v>yes</v>
@@ -1157,13 +1157,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>select_one guardian_rel_list</v>
+        <v>text</v>
       </c>
       <c r="B30" t="str">
-        <v>guardian_relationship</v>
+        <v>guardian_phone</v>
       </c>
       <c r="C30" t="str">
-        <v>Relationship to the young person</v>
+        <v>Parent / guardian phone number</v>
       </c>
       <c r="D30" t="str">
         <v>yes</v>
@@ -1175,21 +1175,21 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v/>
+        <v>regex(., '^[0][7-9][0-1][0-9]{8}$')</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>Enter a valid Nigerian mobile number</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>text</v>
+        <v>select_one yes_no</v>
       </c>
       <c r="B31" t="str">
-        <v>guardian_phone</v>
+        <v>guardian_consent</v>
       </c>
       <c r="C31" t="str">
-        <v>Parent / guardian phone number</v>
+        <v>Does the parent/guardian consent to this registration and to the Registry processing this data (and understand consent may be withdrawn at any time by contacting the Registry)?</v>
       </c>
       <c r="D31" t="str">
         <v>yes</v>
@@ -1201,10 +1201,10 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>regex(., '^[0][7-9][0-1][0-9]{8}$')</v>
+        <v/>
       </c>
       <c r="H31" t="str">
-        <v>Enter a valid Nigerian mobile number</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1212,10 +1212,10 @@
         <v>select_one yes_no</v>
       </c>
       <c r="B32" t="str">
-        <v>guardian_consent</v>
+        <v>is_supervised_apprentice</v>
       </c>
       <c r="C32" t="str">
-        <v>Does the parent/guardian consent to this registration and to the Registry processing this data (and understand consent may be withdrawn at any time by contacting the Registry)?</v>
+        <v>Is this young person a supervised apprentice learning a skill or trade?</v>
       </c>
       <c r="D32" t="str">
         <v>yes</v>
@@ -1235,65 +1235,65 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>select_one yes_no</v>
+        <v>text</v>
       </c>
       <c r="B33" t="str">
-        <v>is_supervised_apprentice</v>
+        <v>apprenticeship_details</v>
       </c>
       <c r="C33" t="str">
-        <v>Is this young person a supervised apprentice learning a skill or trade?</v>
+        <v>Briefly describe the apprenticeship (trade, and supervisor or employer)</v>
       </c>
       <c r="D33" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>${is_supervised_apprentice} = 'yes'</v>
       </c>
       <c r="F33" t="str">
         <v/>
       </c>
       <c r="G33" t="str">
-        <v/>
+        <v>string-length(.) &lt;= 200</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>Maximum 200 characters</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>text</v>
+        <v>end_group</v>
       </c>
       <c r="B34" t="str">
-        <v>apprenticeship_details</v>
+        <v/>
       </c>
       <c r="C34" t="str">
-        <v>Briefly describe the apprenticeship (trade, and supervisor or employer)</v>
+        <v/>
       </c>
       <c r="D34" t="str">
-        <v>no</v>
+        <v/>
       </c>
       <c r="E34" t="str">
-        <v>${is_supervised_apprentice} = 'yes'</v>
+        <v/>
       </c>
       <c r="F34" t="str">
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>string-length(.) &lt;= 200</v>
+        <v/>
       </c>
       <c r="H34" t="str">
-        <v>Maximum 200 characters</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>end_group</v>
+        <v>begin_group</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>grp_skills</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>Skills &amp; Business</v>
       </c>
       <c r="D35" t="str">
         <v/>
@@ -1313,16 +1313,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>begin_group</v>
+        <v>select_multiple skill_list</v>
       </c>
       <c r="B36" t="str">
-        <v>grp_skills</v>
+        <v>skills_possessed</v>
       </c>
       <c r="C36" t="str">
-        <v>Skills &amp; Business</v>
+        <v>Primary Skills (Select all that apply)</v>
       </c>
       <c r="D36" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1339,16 +1339,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>select_multiple skill_list</v>
+        <v>text</v>
       </c>
       <c r="B37" t="str">
-        <v>skills_possessed</v>
+        <v>skills_other</v>
       </c>
       <c r="C37" t="str">
-        <v>Primary Skills (Select all that apply)</v>
+        <v>Other skills not listed above</v>
       </c>
       <c r="D37" t="str">
-        <v>yes</v>
+        <v>no</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1357,24 +1357,24 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v/>
+        <v>string-length(.) &lt;= 200</v>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>Maximum 200 characters</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>text</v>
+        <v>end_group</v>
       </c>
       <c r="B38" t="str">
-        <v>skills_other</v>
+        <v/>
       </c>
       <c r="C38" t="str">
-        <v>Other skills not listed above</v>
+        <v/>
       </c>
       <c r="D38" t="str">
-        <v>no</v>
+        <v/>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1383,21 +1383,21 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>string-length(.) &lt;= 200</v>
+        <v/>
       </c>
       <c r="H38" t="str">
-        <v>Maximum 200 characters</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>end_group</v>
+        <v>begin_group</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>grp_marketplace</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>Public Skills Marketplace</v>
       </c>
       <c r="D39" t="str">
         <v/>
@@ -1417,13 +1417,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>begin_group</v>
+        <v>note</v>
       </c>
       <c r="B40" t="str">
-        <v>grp_marketplace</v>
+        <v>note_marketplace</v>
       </c>
       <c r="C40" t="str">
-        <v>Public Skills Marketplace</v>
+        <v>The OSLSR Skills Marketplace connects skilled workers with employers. You can choose to be listed anonymously or share your contact details.</v>
       </c>
       <c r="D40" t="str">
         <v/>
@@ -1443,16 +1443,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>note</v>
+        <v>select_one yes_no</v>
       </c>
       <c r="B41" t="str">
-        <v>note_marketplace</v>
+        <v>consent_marketplace</v>
       </c>
       <c r="C41" t="str">
-        <v>The OSLSR Skills Marketplace connects skilled workers with employers. You can choose to be listed anonymously or share your contact details.</v>
+        <v>Would you like to join the Anonymous Skills Marketplace? (Your profession, LGA, and experience level will be visible)</v>
       </c>
       <c r="D41" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1472,16 +1472,16 @@
         <v>select_one yes_no</v>
       </c>
       <c r="B42" t="str">
-        <v>consent_marketplace</v>
+        <v>consent_enriched</v>
       </c>
       <c r="C42" t="str">
-        <v>Would you like to join the Anonymous Skills Marketplace? (Your profession, LGA, and experience level will be visible)</v>
+        <v>Would you like employers to see your Name and Phone Number?</v>
       </c>
       <c r="D42" t="str">
         <v>yes</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>${consent_marketplace} = 'yes'</v>
       </c>
       <c r="F42" t="str">
         <v/>
@@ -1495,19 +1495,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>select_one yes_no</v>
+        <v>end_group</v>
       </c>
       <c r="B43" t="str">
-        <v>consent_enriched</v>
+        <v/>
       </c>
       <c r="C43" t="str">
-        <v>Would you like employers to see your Name and Phone Number?</v>
+        <v/>
       </c>
       <c r="D43" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="E43" t="str">
-        <v>${consent_marketplace} = 'yes'</v>
+        <v/>
       </c>
       <c r="F43" t="str">
         <v/>
@@ -1516,38 +1516,12 @@
         <v/>
       </c>
       <c r="H43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>end_group</v>
-      </c>
-      <c r="B44" t="str">
-        <v/>
-      </c>
-      <c r="C44" t="str">
-        <v/>
-      </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-      <c r="F44" t="str">
-        <v/>
-      </c>
-      <c r="G44" t="str">
-        <v/>
-      </c>
-      <c r="H44" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H44"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H43"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4064,7 +4038,7 @@
         <v>oslsr_public_core_v1</v>
       </c>
       <c r="C2" t="str">
-        <v>pubcore-1</v>
+        <v>pubcore-2</v>
       </c>
       <c r="D2" t="str">
         <v>English</v>

--- a/docs/launch-campaign/oslsr-public-core-v1.xlsx
+++ b/docs/launch-campaign/oslsr-public-core-v1.xlsx
@@ -1528,7 +1528,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C225"/>
+  <dimension ref="A1:C267"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3974,40 +3974,502 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>guardian_rel_list</v>
+        <v>skill_list</v>
       </c>
       <c r="B223" t="str">
-        <v>parent</v>
+        <v>veterinary</v>
       </c>
       <c r="C223" t="str">
-        <v>Parent</v>
+        <v>Veterinary/Animal Health Services</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>guardian_rel_list</v>
+        <v>skill_list</v>
       </c>
       <c r="B224" t="str">
-        <v>legal_guardian</v>
+        <v>feed_milling</v>
       </c>
       <c r="C224" t="str">
-        <v>Legal Guardian</v>
+        <v>Animal Feed Milling/Production</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B225" t="str">
+        <v>agric_extension</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Agricultural Extension/Advisory</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B226" t="str">
+        <v>beekeeping</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Beekeeping/Apiculture</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B227" t="str">
+        <v>snail_farming</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Snail/Grasscutter Farming</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B228" t="str">
+        <v>cassava_processing</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Cassava Processing (Garri, Fufu, Lafun)</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B229" t="str">
+        <v>palm_oil_processing</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Palm Oil &amp; Kernel Processing</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B230" t="str">
+        <v>cocoa_farming</v>
+      </c>
+      <c r="C230" t="str">
+        <v>Cocoa Farming &amp; Post-Harvest Handling</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B231" t="str">
+        <v>farm_machinery</v>
+      </c>
+      <c r="C231" t="str">
+        <v>Irrigation &amp; Farm Mechanisation</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B232" t="str">
+        <v>landscaping</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Gardening &amp; Landscaping</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B233" t="str">
+        <v>aso_oke_weaving</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Aso-Oke Weaving</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B234" t="str">
+        <v>adire_dyeing</v>
+      </c>
+      <c r="C234" t="str">
+        <v>Adire &amp; Textile Dyeing</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B235" t="str">
+        <v>woodcarving</v>
+      </c>
+      <c r="C235" t="str">
+        <v>Woodcarving &amp; Sculpture</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B236" t="str">
+        <v>basket_weaving</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Mat &amp; Basket Weaving</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B237" t="str">
+        <v>bronze_casting</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Bronze &amp; Brass Casting</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B238" t="str">
+        <v>pos_agent</v>
+      </c>
+      <c r="C238" t="str">
+        <v>POS Agent &amp; Mobile Money Services</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B239" t="str">
+        <v>market_trading</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Market Trading &amp; Open-Market Selling</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B240" t="str">
+        <v>patent_medicine</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Patent Medicine Vending (PPMV)</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B241" t="str">
+        <v>telecom_retail</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Mobile Recharge &amp; Telecom Retail</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B242" t="str">
+        <v>retail_store</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Supermarket &amp; Retail Store Operation</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B243" t="str">
+        <v>ecommerce_selling</v>
+      </c>
+      <c r="C243" t="str">
+        <v>E-Commerce &amp; Online Selling</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B244" t="str">
+        <v>insurance_sales</v>
+      </c>
+      <c r="C244" t="str">
+        <v>Insurance &amp; Financial Product Sales</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B245" t="str">
+        <v>iron_bending</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Iron Bending &amp; Steel Fixing</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B246" t="str">
+        <v>ceiling_installation</v>
+      </c>
+      <c r="C246" t="str">
+        <v>POP Ceiling &amp; Suspended Ceiling Installation</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B247" t="str">
+        <v>interlocking_paving</v>
+      </c>
+      <c r="C247" t="str">
+        <v>Interlocking Paving &amp; Concrete Work</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B248" t="str">
+        <v>dental_technology</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Dental Technology</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B249" t="str">
+        <v>optometry</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Optometry &amp; Optical Dispensing</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B250" t="str">
+        <v>health_records</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Health Records &amp; Information Management</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B251" t="str">
+        <v>mobile_app_dev</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Mobile App Development</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B252" t="str">
+        <v>it_support</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Networking &amp; IT Support</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B253" t="str">
+        <v>vocational_instruction</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Vocational &amp; Technical Instruction</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B254" t="str">
+        <v>adult_literacy</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Adult Literacy &amp; Non-Formal Education</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B255" t="str">
+        <v>driving_instruction</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Driving Instruction</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B256" t="str">
+        <v>fleet_management</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Fleet Management &amp; Vehicle Tracking</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B257" t="str">
+        <v>cosmetology</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Cosmetology &amp; Skincare</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B258" t="str">
+        <v>gemstone_cutting</v>
+      </c>
+      <c r="C258" t="str">
+        <v>Gemstone Cutting &amp; Polishing</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B259" t="str">
+        <v>petroleum_distribution</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Petroleum Product Distribution</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B260" t="str">
+        <v>lpg_operation</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Gas Plant Operation &amp; LPG Dispensing</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B261" t="str">
+        <v>mc_hype</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Master of Ceremonies (MC) &amp; Hype Services</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B262" t="str">
+        <v>ohs</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Occupational Health &amp; Safety</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B263" t="str">
+        <v>mediation</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Mediation &amp; Alternative Dispute Resolution</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>skill_list</v>
+      </c>
+      <c r="B264" t="str">
+        <v>cooperative_management</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Cooperative &amp; Thrift Society Management</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
         <v>guardian_rel_list</v>
       </c>
-      <c r="B225" t="str">
+      <c r="B265" t="str">
+        <v>parent</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Parent</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>guardian_rel_list</v>
+      </c>
+      <c r="B266" t="str">
+        <v>legal_guardian</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Legal Guardian</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>guardian_rel_list</v>
+      </c>
+      <c r="B267" t="str">
         <v>other</v>
       </c>
-      <c r="C225" t="str">
+      <c r="C267" t="str">
         <v>Other (relative or caregiver)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C225"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C267"/>
   </ignoredErrors>
 </worksheet>
 </file>
